--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brunworg\Source\Workspaces\genBOE\dev\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369B3392-0ACE-47E8-82E4-77E7CB36913A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19035" windowHeight="10755" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -21,20 +22,25 @@
     <sheet name="BOEs" sheetId="16" r:id="rId7"/>
     <sheet name="BOE Status" sheetId="23" r:id="rId8"/>
     <sheet name="Resource Spreads" sheetId="41" r:id="rId9"/>
-    <sheet name="WBS" sheetId="24" r:id="rId10"/>
-    <sheet name="User Permissions" sheetId="39" r:id="rId11"/>
-    <sheet name="CLINs" sheetId="25" r:id="rId12"/>
-    <sheet name="Workspace Identification" sheetId="40" r:id="rId13"/>
+    <sheet name="MOQ by BOE by Task" sheetId="43" r:id="rId10"/>
+    <sheet name="MOQ Table Data" sheetId="44" r:id="rId11"/>
+    <sheet name="MOQ Summary" sheetId="45" r:id="rId12"/>
+    <sheet name="WBS" sheetId="24" r:id="rId13"/>
+    <sheet name="User Permissions" sheetId="39" r:id="rId14"/>
+    <sheet name="CLINs" sheetId="25" r:id="rId15"/>
+    <sheet name="Workspace Identification" sheetId="40" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AP$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AQ$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -44,22 +50,32 @@
     <definedName name="SpreadCurve">[2]Lists!$C$2:$C$52</definedName>
     <definedName name="WBS">'[1]Options Lists'!$A$2:$A$8</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId16"/>
-    <pivotCache cacheId="4" r:id="rId17"/>
-    <pivotCache cacheId="5" r:id="rId18"/>
+    <pivotCache cacheId="0" r:id="rId19"/>
+    <pivotCache cacheId="1" r:id="rId20"/>
+    <pivotCache cacheId="2" r:id="rId21"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Lindsay Yorks</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -78,12 +94,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -98,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
       <text>
         <r>
           <rPr>
@@ -112,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
       <text>
         <r>
           <rPr>
@@ -125,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
           <rPr>
@@ -145,12 +161,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -165,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -179,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000003000000}">
       <text>
         <r>
           <rPr>
@@ -192,7 +208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000004000000}">
       <text>
         <r>
           <rPr>
@@ -245,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000005000000}">
       <text>
         <r>
           <rPr>
@@ -303,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="145">
   <si>
     <t>Start Date</t>
   </si>
@@ -693,19 +709,64 @@
   </si>
   <si>
     <t>Subcontractor Admin</t>
+  </si>
+  <si>
+    <t>Total MOQ Hours</t>
+  </si>
+  <si>
+    <t>Table Name</t>
+  </si>
+  <si>
+    <t>Period of Performance (PoP): Start Date</t>
+  </si>
+  <si>
+    <t>Period of Performance (PoP): End Date</t>
+  </si>
+  <si>
+    <t>Repository Name</t>
+  </si>
+  <si>
+    <t>Query Type (Weekly/Monthly)</t>
+  </si>
+  <si>
+    <t>Date of Report</t>
+  </si>
+  <si>
+    <t>Historical Program Name</t>
+  </si>
+  <si>
+    <t>Contract Number</t>
+  </si>
+  <si>
+    <t>WBS/WBS Element</t>
+  </si>
+  <si>
+    <t>Total WBS/WBS Element Hours</t>
+  </si>
+  <si>
+    <t>Additional Query Filters (i.e. cost number, employee id)</t>
+  </si>
+  <si>
+    <t>Total Relevant Hours After Additional Query Filters Applied</t>
+  </si>
+  <si>
+    <t>MOQ Hours Bid/Spread</t>
+  </si>
+  <si>
+    <t>% of total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -747,8 +808,36 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFECF0F1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFECF0F1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF452DB2"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -764,6 +853,36 @@
           <color theme="0" tint="-0.25098422193060094"/>
         </stop>
       </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF070729"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9F9F9F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF452DB2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD35714"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -801,11 +920,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -910,9 +1035,15 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="genBOE" xfId="1"/>
+  <cellStyles count="8">
+    <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="PPDuplicateRow" xfId="5" xr:uid="{3A917E72-87DA-446C-88B4-228FF55097D8}"/>
+    <cellStyle name="PPHeaderColumn" xfId="3" xr:uid="{83B08EAB-896F-4E60-9F22-2139D539C349}"/>
+    <cellStyle name="PPHeaderRequired" xfId="4" xr:uid="{282AF6C9-0E84-4678-AE7D-D9BEBE2F943A}"/>
+    <cellStyle name="PPHeaderTop" xfId="2" xr:uid="{C93226A2-FFA8-470F-9430-4474209C6796}"/>
+    <cellStyle name="PPInvalidValue" xfId="6" xr:uid="{06E678D2-08B9-4E66-A058-37087CC702EF}"/>
+    <cellStyle name="PPMissingValue" xfId="7" xr:uid="{354CBC8A-3A2B-4AAE-8DDE-938AA9CC49E2}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2778,7 +2909,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.71514803241" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.71514803241" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N16" sheet="BOEs (3)"/>
   </cacheSource>
@@ -2893,7 +3024,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:AP1" sheet="BOEs"/>
   </cacheSource>
@@ -3040,7 +3171,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40654.464705439816" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40654.464705439816" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF05000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:T16" sheet="BOEs (2)"/>
   </cacheSource>
@@ -4099,7 +4230,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4448,7 +4579,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4657,7 +4788,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -5419,7 +5550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:N32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5938,7 +6069,161 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="61.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:Q1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD4E4A2D-06CE-42AF-A96E-0F577DD1FCDB}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -5974,8 +6259,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6027,8 +6312,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -6069,8 +6354,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6168,7 +6453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6729,14 +7014,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:N16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6897,7 +7182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:T32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7570,7 +7855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:T16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8067,14 +8352,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:T16"/>
+  <autoFilter ref="B1:T16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8254,14 +8539,14 @@
     </row>
     <row r="2" spans="1:42" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AP1"/>
+  <autoFilter ref="A1:AP1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8438,7 +8723,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AQ1"/>
+  <autoFilter ref="A1:AQ1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -8446,7 +8731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -8517,7 +8802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8583,35 +8868,13 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8714,32 +8977,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8756,4 +9016,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369B3392-0ACE-47E8-82E4-77E7CB36913A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBAA886-7FC9-4148-9EFB-AD5BDAE38AED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId19"/>
-    <pivotCache cacheId="1" r:id="rId20"/>
-    <pivotCache cacheId="2" r:id="rId21"/>
+    <pivotCache cacheId="9" r:id="rId19"/>
+    <pivotCache cacheId="10" r:id="rId20"/>
+    <pivotCache cacheId="11" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3026,7 +3026,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B1:AP1" sheet="BOEs"/>
+    <worksheetSource ref="C1:AP1" sheet="BOEs"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Type" numFmtId="49">
@@ -4230,7 +4230,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4579,7 +4579,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4788,7 +4788,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8365,19 +8365,19 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" style="36" customWidth="1"/>
     <col min="16" max="16" width="12.5703125" style="36" customWidth="1"/>
     <col min="17" max="17" width="21.42578125" style="1" customWidth="1"/>
@@ -8414,43 +8414,43 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="O1" s="35" t="s">
         <v>31</v>
@@ -8552,9 +8552,9 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -8595,16 +8595,16 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>29</v>
@@ -8875,6 +8875,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8977,15 +8986,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
@@ -9000,6 +9000,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9014,14 +9022,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBAA886-7FC9-4148-9EFB-AD5BDAE38AED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD718BDA-BCC8-4FBD-9694-69CA25128284}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId19"/>
-    <pivotCache cacheId="10" r:id="rId20"/>
-    <pivotCache cacheId="11" r:id="rId21"/>
+    <pivotCache cacheId="54" r:id="rId19"/>
+    <pivotCache cacheId="55" r:id="rId20"/>
+    <pivotCache cacheId="56" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4230,7 +4230,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4579,7 +4579,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4788,7 +4788,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8884,6 +8884,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8986,19 +8999,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
@@ -9008,6 +9008,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9024,21 +9041,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD718BDA-BCC8-4FBD-9694-69CA25128284}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11FCC27-9B68-497E-AC26-B80E22F0FC9E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="54" r:id="rId19"/>
-    <pivotCache cacheId="55" r:id="rId20"/>
-    <pivotCache cacheId="56" r:id="rId21"/>
+    <pivotCache cacheId="6" r:id="rId19"/>
+    <pivotCache cacheId="7" r:id="rId20"/>
+    <pivotCache cacheId="8" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -319,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="144">
   <si>
     <t>Start Date</t>
   </si>
@@ -733,9 +733,6 @@
   </si>
   <si>
     <t>Historical Program Name</t>
-  </si>
-  <si>
-    <t>Contract Number</t>
   </si>
   <si>
     <t>WBS/WBS Element</t>
@@ -4230,7 +4227,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4579,7 +4576,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4788,7 +4785,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6113,7 +6110,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6126,16 +6123,15 @@
     <col min="8" max="8" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="42" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6170,13 +6166,13 @@
         <v>138</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>140</v>
@@ -6184,13 +6180,10 @@
       <c r="P1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
+  <autoFilter ref="A1:P1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6210,10 +6203,10 @@
         <v>85</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -8552,7 +8545,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -8875,15 +8868,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -8894,6 +8878,15 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9000,14 +8993,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9020,6 +9005,14 @@
     <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11FCC27-9B68-497E-AC26-B80E22F0FC9E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDD0106-7D79-4634-88B3-66DDF8F23CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId19"/>
-    <pivotCache cacheId="7" r:id="rId20"/>
-    <pivotCache cacheId="8" r:id="rId21"/>
+    <pivotCache cacheId="30" r:id="rId19"/>
+    <pivotCache cacheId="31" r:id="rId20"/>
+    <pivotCache cacheId="32" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -757,11 +757,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -929,7 +930,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
@@ -1031,6 +1032,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4227,7 +4232,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4576,7 +4581,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4785,7 +4790,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6195,7 +6200,7 @@
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6205,7 +6210,7 @@
       <c r="B1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="39" t="s">
         <v>143</v>
       </c>
     </row>
@@ -8868,28 +8873,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8992,32 +8975,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9034,4 +9014,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDD0106-7D79-4634-88B3-66DDF8F23CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC460066-7B75-41A0-9A23-5EAAC30EEF42}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="30" r:id="rId19"/>
-    <pivotCache cacheId="31" r:id="rId20"/>
-    <pivotCache cacheId="32" r:id="rId21"/>
+    <pivotCache cacheId="0" r:id="rId19"/>
+    <pivotCache cacheId="1" r:id="rId20"/>
+    <pivotCache cacheId="2" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -319,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="143">
   <si>
     <t>Start Date</t>
   </si>
@@ -736,9 +736,6 @@
   </si>
   <si>
     <t>WBS/WBS Element</t>
-  </si>
-  <si>
-    <t>Total WBS/WBS Element Hours</t>
   </si>
   <si>
     <t>Additional Query Filters (i.e. cost number, employee id)</t>
@@ -4232,7 +4229,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4581,7 +4578,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4790,7 +4787,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6115,7 +6112,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6131,12 +6128,11 @@
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6182,13 +6178,10 @@
       <c r="O1" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
+  <autoFilter ref="A1:O1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6208,10 +6201,10 @@
         <v>85</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="39" t="s">
         <v>142</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -8873,6 +8866,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8975,29 +8990,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9014,29 +9032,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDD0106-7D79-4634-88B3-66DDF8F23CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEC9F69-AFB5-44C1-AA6D-16B260EF9879}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="345" windowWidth="18900" windowHeight="11055" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -52,9 +52,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="30" r:id="rId19"/>
-    <pivotCache cacheId="31" r:id="rId20"/>
-    <pivotCache cacheId="32" r:id="rId21"/>
+    <pivotCache cacheId="0" r:id="rId19"/>
+    <pivotCache cacheId="1" r:id="rId20"/>
+    <pivotCache cacheId="2" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -741,16 +741,16 @@
     <t>Total WBS/WBS Element Hours</t>
   </si>
   <si>
-    <t>Additional Query Filters (i.e. cost number, employee id)</t>
-  </si>
-  <si>
-    <t>Total Relevant Hours After Additional Query Filters Applied</t>
-  </si>
-  <si>
     <t>MOQ Hours Bid/Spread</t>
   </si>
   <si>
     <t>% of total</t>
+  </si>
+  <si>
+    <t>Employee ID Filters</t>
+  </si>
+  <si>
+    <t>Total Relevant Hours After Employee ID Filters Applied</t>
   </si>
 </sst>
 </file>
@@ -4232,7 +4232,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4581,7 +4581,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4790,7 +4790,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6180,10 +6180,10 @@
         <v>139</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6208,10 +6208,10 @@
         <v>85</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -8873,6 +8873,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8975,29 +8997,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9014,29 +9039,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEC9F69-AFB5-44C1-AA6D-16B260EF9879}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCEE1A4-3B32-4CB3-BCCA-3970DCDAC196}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="345" windowWidth="18900" windowHeight="11055" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="690" windowWidth="18900" windowHeight="11055" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -24,15 +24,14 @@
     <sheet name="Resource Spreads" sheetId="41" r:id="rId9"/>
     <sheet name="MOQ by BOE by Task" sheetId="43" r:id="rId10"/>
     <sheet name="MOQ Table Data" sheetId="44" r:id="rId11"/>
-    <sheet name="MOQ Summary" sheetId="45" r:id="rId12"/>
-    <sheet name="WBS" sheetId="24" r:id="rId13"/>
-    <sheet name="User Permissions" sheetId="39" r:id="rId14"/>
-    <sheet name="CLINs" sheetId="25" r:id="rId15"/>
-    <sheet name="Workspace Identification" sheetId="40" r:id="rId16"/>
+    <sheet name="WBS" sheetId="24" r:id="rId12"/>
+    <sheet name="User Permissions" sheetId="39" r:id="rId13"/>
+    <sheet name="CLINs" sheetId="25" r:id="rId14"/>
+    <sheet name="Workspace Identification" sheetId="40" r:id="rId15"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AP$1</definedName>
@@ -52,9 +51,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId19"/>
-    <pivotCache cacheId="1" r:id="rId20"/>
-    <pivotCache cacheId="2" r:id="rId21"/>
+    <pivotCache cacheId="3" r:id="rId18"/>
+    <pivotCache cacheId="4" r:id="rId19"/>
+    <pivotCache cacheId="5" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -319,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="142">
   <si>
     <t>Start Date</t>
   </si>
@@ -739,12 +738,6 @@
   </si>
   <si>
     <t>Total WBS/WBS Element Hours</t>
-  </si>
-  <si>
-    <t>MOQ Hours Bid/Spread</t>
-  </si>
-  <si>
-    <t>% of total</t>
   </si>
   <si>
     <t>Employee ID Filters</t>
@@ -757,12 +750,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -930,7 +922,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
@@ -1032,10 +1024,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4232,7 +4220,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4581,7 +4569,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4790,7 +4778,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6180,10 +6168,10 @@
         <v>139</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6194,33 +6182,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD4E4A2D-06CE-42AF-A96E-0F577DD1FCDB}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="40" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
@@ -6257,7 +6218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
@@ -6310,7 +6271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
@@ -6352,7 +6313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A17"/>
@@ -8873,28 +8834,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8997,32 +8936,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9039,4 +8975,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBOE\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCEE1A4-3B32-4CB3-BCCA-3970DCDAC196}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69260E37-9976-40B5-9ED1-39C416491D33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="690" windowWidth="18900" windowHeight="11055" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="975" yWindow="-120" windowWidth="27945" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -38,8 +38,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AQ$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -51,9 +51,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId18"/>
-    <pivotCache cacheId="4" r:id="rId19"/>
-    <pivotCache cacheId="5" r:id="rId20"/>
+    <pivotCache cacheId="6" r:id="rId18"/>
+    <pivotCache cacheId="7" r:id="rId19"/>
+    <pivotCache cacheId="8" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="140">
   <si>
     <t>Start Date</t>
   </si>
@@ -710,9 +710,6 @@
     <t>Subcontractor Admin</t>
   </si>
   <si>
-    <t>Total MOQ Hours</t>
-  </si>
-  <si>
     <t>Table Name</t>
   </si>
   <si>
@@ -735,9 +732,6 @@
   </si>
   <si>
     <t>WBS/WBS Element</t>
-  </si>
-  <si>
-    <t>Total WBS/WBS Element Hours</t>
   </si>
   <si>
     <t>Employee ID Filters</t>
@@ -4220,7 +4214,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4569,7 +4563,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4778,7 +4772,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6060,18 +6054,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
-    <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6088,22 +6081,19 @@
         <v>123</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
+  <autoFilter ref="A1:F1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6119,12 +6109,11 @@
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6141,42 +6130,39 @@
         <v>85</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
+  <autoFilter ref="A1:O1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8834,6 +8820,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8936,15 +8931,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
@@ -8959,6 +8945,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8973,14 +8967,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBOE\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69260E37-9976-40B5-9ED1-39C416491D33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B63D83-CC6B-47F5-8D31-A865E899540F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="-120" windowWidth="27945" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -51,9 +51,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId18"/>
-    <pivotCache cacheId="7" r:id="rId19"/>
-    <pivotCache cacheId="8" r:id="rId20"/>
+    <pivotCache cacheId="0" r:id="rId18"/>
+    <pivotCache cacheId="1" r:id="rId19"/>
+    <pivotCache cacheId="2" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="141">
   <si>
     <t>Start Date</t>
   </si>
@@ -738,6 +738,9 @@
   </si>
   <si>
     <t>Total Relevant Hours After Employee ID Filters Applied</t>
+  </si>
+  <si>
+    <t>MOQ Table Custom Field</t>
   </si>
 </sst>
 </file>
@@ -4214,7 +4217,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4563,7 +4566,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4772,7 +4775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6093,7 +6096,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6111,9 +6114,10 @@
     <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6159,10 +6163,13 @@
       <c r="O1" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="P1" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{9A7F204E-ACEF-43F5-B840-26856445FC24}"/>
+  <autoFilter ref="A1:P1" xr:uid="{00943D54-A2BA-4F5E-85E1-C57F6D83B824}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8829,6 +8836,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8931,19 +8951,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
@@ -8953,6 +8960,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8969,21 +8993,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B63D83-CC6B-47F5-8D31-A865E899540F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DC01BB-7BB7-42AF-B206-52ABC7528514}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6112,9 +6112,9 @@
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6158,19 +6158,20 @@
         <v>132</v>
       </c>
       <c r="N1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{00943D54-A2BA-4F5E-85E1-C57F6D83B824}"/>
+  <autoFilter ref="A1:P1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBoe\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DC01BB-7BB7-42AF-B206-52ABC7528514}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12655BD6-BD0C-43BE-AB4F-C4E2A297432C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15990" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
@@ -51,9 +51,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId18"/>
-    <pivotCache cacheId="1" r:id="rId19"/>
-    <pivotCache cacheId="2" r:id="rId20"/>
+    <pivotCache cacheId="6" r:id="rId18"/>
+    <pivotCache cacheId="7" r:id="rId19"/>
+    <pivotCache cacheId="8" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4217,7 +4217,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4566,7 +4566,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4775,7 +4775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6099,22 +6099,22 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6158,18 +6158,18 @@
         <v>132</v>
       </c>
       <c r="N1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
+  <autoFilter ref="A1:O1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -8828,15 +8828,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -8847,6 +8838,15 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8953,14 +8953,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8973,6 +8965,14 @@
     <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBoe\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Desktop\Code-Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12655BD6-BD0C-43BE-AB4F-C4E2A297432C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2423CD5E-B72C-433C-9110-4C1196E70316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -51,9 +51,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId18"/>
-    <pivotCache cacheId="7" r:id="rId19"/>
-    <pivotCache cacheId="8" r:id="rId20"/>
+    <pivotCache cacheId="0" r:id="rId18"/>
+    <pivotCache cacheId="1" r:id="rId19"/>
+    <pivotCache cacheId="2" r:id="rId20"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="142">
   <si>
     <t>Start Date</t>
   </si>
@@ -741,6 +741,9 @@
   </si>
   <si>
     <t>MOQ Table Custom Field</t>
+  </si>
+  <si>
+    <t>SAP Connection Enabled</t>
   </si>
 </sst>
 </file>
@@ -4217,7 +4220,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4566,7 +4569,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4775,7 +4778,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6310,7 +6313,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" style="1" customWidth="1"/>
@@ -6397,6 +6400,11 @@
     <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Desktop\Code-Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2423CD5E-B72C-433C-9110-4C1196E70316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCC767-93A7-4B8E-B8C3-EAB593CBA101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -8836,6 +8836,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -8846,15 +8855,6 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8961,6 +8961,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8973,14 +8981,6 @@
     <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Desktop\Code-Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e302876\proph\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCC767-93A7-4B8E-B8C3-EAB593CBA101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9092E267-DA95-4EC9-A776-BC8ED9C3BA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -34,13 +34,13 @@
     <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AP$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AQ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AT$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$P$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
     <definedName name="CLINs">'[1]Options Lists'!$B$2:$B$5</definedName>
@@ -55,6 +55,7 @@
     <pivotCache cacheId="1" r:id="rId19"/>
     <pivotCache cacheId="2" r:id="rId20"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -318,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="146">
   <si>
     <t>Start Date</t>
   </si>
@@ -744,6 +745,18 @@
   </si>
   <si>
     <t>SAP Connection Enabled</t>
+  </si>
+  <si>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>BRC Description</t>
+  </si>
+  <si>
+    <t>BRC Type</t>
+  </si>
+  <si>
+    <t>BRC Segment Region</t>
   </si>
 </sst>
 </file>
@@ -3016,7 +3029,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:AP1" sheet="BOEs"/>
+    <worksheetSource ref="C1:AT1" sheet="BOEs"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Type" numFmtId="49">
@@ -5543,25 +5556,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:N32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
@@ -5605,7 +5618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -5649,7 +5662,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G6" t="s">
         <v>57</v>
       </c>
@@ -5675,7 +5688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H8" t="s">
         <v>43</v>
       </c>
@@ -5698,7 +5711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>62</v>
       </c>
@@ -5733,7 +5746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G12" t="s">
         <v>57</v>
       </c>
@@ -5759,7 +5772,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H14" t="s">
         <v>43</v>
       </c>
@@ -5782,7 +5795,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>57</v>
       </c>
@@ -5817,7 +5830,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -5861,7 +5874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G20" t="s">
         <v>57</v>
       </c>
@@ -5887,7 +5900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H22" t="s">
         <v>43</v>
       </c>
@@ -5910,7 +5923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H24" t="s">
         <v>55</v>
       </c>
@@ -5933,7 +5946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H26" t="s">
         <v>51</v>
       </c>
@@ -5956,7 +5969,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
         <v>64</v>
       </c>
@@ -5991,7 +6004,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G30" t="s">
         <v>57</v>
       </c>
@@ -6017,7 +6030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
         <v>62</v>
       </c>
@@ -6055,22 +6068,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6090,37 +6107,41 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6170,11 +6191,15 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6182,15 +6207,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="4" width="30.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="33.140625" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="30.6640625" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="30.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
@@ -6207,10 +6232,14 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:5" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6219,20 +6248,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
-    <col min="2" max="3" width="35.7109375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="18.88671875" style="15" customWidth="1"/>
+    <col min="2" max="3" width="35.6640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="14" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="14" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -6261,10 +6290,14 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6272,17 +6305,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" style="8" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="13.109375" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="8" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>99</v>
       </c>
@@ -6302,10 +6335,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6314,95 +6351,95 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="82.140625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="82.109375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>141</v>
       </c>
@@ -6410,6 +6447,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6417,28 +6458,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13.5703125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="3"/>
+    <col min="15" max="17" width="13.5546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -6482,7 +6523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>59</v>
       </c>
@@ -6493,7 +6534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>59</v>
       </c>
@@ -6516,7 +6557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -6557,7 +6598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
@@ -6598,7 +6639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>59</v>
       </c>
@@ -6621,7 +6662,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>59</v>
       </c>
@@ -6662,7 +6703,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
@@ -6703,7 +6744,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -6723,7 +6764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
@@ -6746,7 +6787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>60</v>
       </c>
@@ -6787,7 +6828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>60</v>
       </c>
@@ -6828,7 +6869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -6869,7 +6910,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
@@ -6910,7 +6951,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>60</v>
       </c>
@@ -6933,7 +6974,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>60</v>
       </c>
@@ -6978,6 +7019,10 @@
   <autoFilter ref="A1:N16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6985,20 +7030,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" customWidth="1"/>
     <col min="9" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -7024,7 +7069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -7050,7 +7095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -7058,7 +7103,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7084,12 +7129,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>45</v>
       </c>
@@ -7097,7 +7142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -7123,12 +7168,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>45</v>
       </c>
@@ -7139,6 +7184,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -7146,29 +7195,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:T32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
@@ -7230,7 +7279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -7292,7 +7341,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>34</v>
       </c>
@@ -7351,7 +7400,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="I8" t="s">
         <v>40</v>
       </c>
@@ -7389,7 +7438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -7448,7 +7497,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="R12" t="s">
         <v>20</v>
       </c>
@@ -7459,7 +7508,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N14" t="s">
         <v>43</v>
       </c>
@@ -7482,7 +7531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="O16" t="s">
         <v>53</v>
       </c>
@@ -7502,7 +7551,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -7564,7 +7613,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -7623,7 +7672,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="I22" t="s">
         <v>49</v>
       </c>
@@ -7661,7 +7710,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -7720,7 +7769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="O26" t="s">
         <v>52</v>
       </c>
@@ -7740,7 +7789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N28" t="s">
         <v>43</v>
       </c>
@@ -7763,7 +7812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N30" t="s">
         <v>55</v>
       </c>
@@ -7786,7 +7835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="N32" t="s">
         <v>51</v>
       </c>
@@ -7812,6 +7861,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -7819,33 +7872,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:T16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="3" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="3" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13.5703125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="3"/>
+    <col min="21" max="23" width="13.5546875" style="3" customWidth="1"/>
+    <col min="24" max="24" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>70</v>
       </c>
@@ -7907,7 +7960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>58</v>
       </c>
@@ -7933,7 +7986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
@@ -7956,7 +8009,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
@@ -7985,7 +8038,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>58</v>
       </c>
@@ -8014,7 +8067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>58</v>
       </c>
@@ -8037,7 +8090,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -8066,7 +8119,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -8095,7 +8148,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -8121,7 +8174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -8144,7 +8197,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -8173,7 +8226,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -8202,7 +8255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -8231,7 +8284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -8260,7 +8313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -8283,7 +8336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -8316,61 +8369,66 @@
   <autoFilter ref="B1:T16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AP2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AT2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="36" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="36" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="31" customWidth="1"/>
-    <col min="19" max="19" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="36" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="31" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" style="36" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="36" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20.109375" style="31" customWidth="1"/>
+    <col min="19" max="19" width="18.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.6640625" style="36" customWidth="1"/>
+    <col min="24" max="24" width="12.88671875" style="36" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="20.44140625" style="31" customWidth="1"/>
     <col min="27" max="27" width="19" style="29" customWidth="1"/>
     <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.28515625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.85546875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.85546875" style="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="33" customWidth="1"/>
-    <col min="36" max="36" width="17" style="31" customWidth="1"/>
-    <col min="37" max="37" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.7109375" style="38" customWidth="1"/>
-    <col min="40" max="40" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.7109375" style="29" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="29" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.33203125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="18.5546875" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.88671875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.88671875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="33" customWidth="1"/>
+    <col min="40" max="40" width="17" style="31" customWidth="1"/>
+    <col min="41" max="41" width="15.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.6640625" style="38" customWidth="1"/>
+    <col min="44" max="44" width="10.5546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.6640625" style="29" customWidth="1"/>
+    <col min="47" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8465,93 +8523,110 @@
         <v>106</v>
       </c>
       <c r="AF1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AI1" s="32" t="s">
+      <c r="AM1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="AJ1" s="30" t="s">
+      <c r="AN1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AK1" s="24" t="s">
+      <c r="AO1" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="AM1" s="37" t="s">
+      <c r="AQ1" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="AN1" s="37" t="s">
+      <c r="AR1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AO1" s="34" t="s">
+      <c r="AS1" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="AP1" s="27" t="s">
+      <c r="AT1" s="27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:46" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:AT1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AU2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="20.140625" style="25" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="20.109375" style="25" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="25" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="24.7109375" style="3" customWidth="1"/>
-    <col min="32" max="32" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="18.85546875" style="3" customWidth="1"/>
-    <col min="37" max="37" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13" style="20" customWidth="1"/>
-    <col min="42" max="42" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="3"/>
+    <col min="21" max="21" width="21.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.6640625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="20.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.44140625" style="25" customWidth="1"/>
+    <col min="27" max="27" width="20.44140625" style="3" customWidth="1"/>
+    <col min="28" max="28" width="24.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="24.6640625" style="3" customWidth="1"/>
+    <col min="32" max="35" width="18.5546875" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="18.88671875" style="3" customWidth="1"/>
+    <col min="41" max="41" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13" style="20" customWidth="1"/>
+    <col min="46" max="46" width="17" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="24.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="48" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8646,47 +8721,63 @@
         <v>106</v>
       </c>
       <c r="AF1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AS1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="24" t="s">
+      <c r="AT1" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:47" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:AQ1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8695,23 +8786,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="7" customWidth="1"/>
-    <col min="2" max="3" width="25.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="7" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="25.7109375" style="7" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="7" customWidth="1"/>
+    <col min="2" max="3" width="25.6640625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" style="7" customWidth="1"/>
+    <col min="6" max="7" width="15.6640625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="25.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" style="7" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="7"/>
+    <col min="15" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>27</v>
       </c>
@@ -8755,35 +8846,40 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:14" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="16" customWidth="1"/>
     <col min="2" max="2" width="24" style="16" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5703125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" style="17" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" style="23" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" style="28" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="16"/>
+    <col min="3" max="3" width="25.5546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5546875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="16" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.109375" style="16" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.6640625" style="17" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="23" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" style="28" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -8812,52 +8908,40 @@
         <v>89</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="P1" s="27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:N2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:P2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -8960,32 +9044,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9002,4 +9083,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e302876\proph\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9092E267-DA95-4EC9-A776-BC8ED9C3BA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F0BEF8-9FD7-422B-A399-28F0D1D122D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -55,7 +55,6 @@
     <pivotCache cacheId="1" r:id="rId19"/>
     <pivotCache cacheId="2" r:id="rId20"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1062,7 +1061,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BOEs"/>
@@ -1143,7 +1142,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Labor Types"/>
@@ -5234,9 +5233,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5274,9 +5273,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5309,26 +5308,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5361,26 +5343,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8942,6 +8907,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9044,29 +9031,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9083,29 +9073,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e302876\proph\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBoe\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F0BEF8-9FD7-422B-A399-28F0D1D122D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808C1457-7E6E-4AE4-847B-F90120CE08B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22305" yWindow="15" windowWidth="34035" windowHeight="21570" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="147">
   <si>
     <t>Start Date</t>
   </si>
@@ -756,6 +756,9 @@
   </si>
   <si>
     <t>BRC Segment Region</t>
+  </si>
+  <si>
+    <t>Rationale</t>
   </si>
 </sst>
 </file>
@@ -5521,25 +5524,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:N32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
@@ -5583,7 +5586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -5627,7 +5630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>57</v>
       </c>
@@ -5653,7 +5656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H8" t="s">
         <v>43</v>
       </c>
@@ -5676,7 +5679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>62</v>
       </c>
@@ -5711,7 +5714,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
         <v>57</v>
       </c>
@@ -5737,7 +5740,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>43</v>
       </c>
@@ -5760,7 +5763,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>57</v>
       </c>
@@ -5795,7 +5798,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -5839,7 +5842,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>57</v>
       </c>
@@ -5865,7 +5868,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H22" t="s">
         <v>43</v>
       </c>
@@ -5888,7 +5891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
         <v>55</v>
       </c>
@@ -5911,7 +5914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H26" t="s">
         <v>51</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
         <v>64</v>
       </c>
@@ -5969,7 +5972,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G30" t="s">
         <v>57</v>
       </c>
@@ -5995,7 +5998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>62</v>
       </c>
@@ -6042,17 +6045,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="40.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6071,8 +6075,11 @@
       <c r="F1" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="G1" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6086,27 +6093,27 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6156,7 +6163,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6172,15 +6179,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="4" width="30.6640625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="33.109375" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="30.7109375" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="30.7109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.140625" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
@@ -6197,7 +6204,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:5" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6213,20 +6220,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="15" customWidth="1"/>
-    <col min="2" max="3" width="35.6640625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="26.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="15"/>
+    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
+    <col min="2" max="3" width="35.7109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="14" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="14" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -6255,7 +6262,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6270,17 +6277,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="8" customWidth="1"/>
-    <col min="4" max="5" width="20.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="13.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" style="8" customWidth="1"/>
+    <col min="4" max="5" width="20.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>99</v>
       </c>
@@ -6300,7 +6307,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6316,95 +6323,95 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="82.109375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="32.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>141</v>
       </c>
@@ -6423,28 +6430,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13.5546875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="3"/>
+    <col min="15" max="17" width="13.5703125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -6488,7 +6495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>59</v>
       </c>
@@ -6499,7 +6506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>59</v>
       </c>
@@ -6522,7 +6529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -6563,7 +6570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
@@ -6604,7 +6611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>59</v>
       </c>
@@ -6627,7 +6634,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>59</v>
       </c>
@@ -6668,7 +6675,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
@@ -6709,7 +6716,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -6729,7 +6736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
@@ -6752,7 +6759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>60</v>
       </c>
@@ -6793,7 +6800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>60</v>
       </c>
@@ -6834,7 +6841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -6875,7 +6882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
@@ -6916,7 +6923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>60</v>
       </c>
@@ -6939,7 +6946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>60</v>
       </c>
@@ -6995,20 +7002,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" customWidth="1"/>
     <col min="9" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -7034,7 +7041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -7060,7 +7067,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -7068,7 +7075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7094,12 +7101,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>45</v>
       </c>
@@ -7107,7 +7114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -7133,12 +7140,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>45</v>
       </c>
@@ -7160,29 +7167,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:T32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
@@ -7244,7 +7251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -7306,7 +7313,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>34</v>
       </c>
@@ -7365,7 +7372,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I8" t="s">
         <v>40</v>
       </c>
@@ -7403,7 +7410,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -7462,7 +7469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R12" t="s">
         <v>20</v>
       </c>
@@ -7473,7 +7480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N14" t="s">
         <v>43</v>
       </c>
@@ -7496,7 +7503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="O16" t="s">
         <v>53</v>
       </c>
@@ -7516,7 +7523,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -7578,7 +7585,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -7637,7 +7644,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
         <v>49</v>
       </c>
@@ -7675,7 +7682,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -7734,7 +7741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="O26" t="s">
         <v>52</v>
       </c>
@@ -7754,7 +7761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N28" t="s">
         <v>43</v>
       </c>
@@ -7777,7 +7784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N30" t="s">
         <v>55</v>
       </c>
@@ -7800,7 +7807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N32" t="s">
         <v>51</v>
       </c>
@@ -7837,33 +7844,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:T16"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="3" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="3" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13.5546875" style="3" customWidth="1"/>
-    <col min="24" max="24" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.109375" style="3"/>
+    <col min="21" max="23" width="13.5703125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>70</v>
       </c>
@@ -7925,7 +7932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>58</v>
       </c>
@@ -7951,7 +7958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
@@ -7974,7 +7981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
@@ -8003,7 +8010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>58</v>
       </c>
@@ -8032,7 +8039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>58</v>
       </c>
@@ -8055,7 +8062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -8084,7 +8091,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -8113,7 +8120,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -8139,7 +8146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -8162,7 +8169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -8191,7 +8198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -8220,7 +8227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -8249,7 +8256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -8278,7 +8285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -8301,7 +8308,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -8345,55 +8352,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AT2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" style="36" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="36" customWidth="1"/>
-    <col min="17" max="17" width="21.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.109375" style="31" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.6640625" style="36" customWidth="1"/>
-    <col min="24" max="24" width="12.88671875" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.44140625" style="31" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="36" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="36" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" style="31" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" style="36" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="31" customWidth="1"/>
     <col min="27" max="27" width="19" style="29" customWidth="1"/>
     <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.33203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="18.5546875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.88671875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.88671875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.28515625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.85546875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.85546875" style="1" customWidth="1"/>
     <col min="39" max="39" width="13" style="33" customWidth="1"/>
     <col min="40" max="40" width="17" style="31" customWidth="1"/>
-    <col min="41" max="41" width="15.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.6640625" style="38" customWidth="1"/>
-    <col min="44" max="44" width="10.5546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.7109375" style="38" customWidth="1"/>
+    <col min="44" max="44" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.6640625" style="29" customWidth="1"/>
-    <col min="47" max="16384" width="9.109375" style="1"/>
+    <col min="46" max="46" width="8.7109375" style="29" customWidth="1"/>
+    <col min="47" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8533,7 +8540,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:46" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:AT1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8549,49 +8556,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AU2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="20.109375" style="25" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="20.140625" style="25" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.6640625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="20.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.44140625" style="25" customWidth="1"/>
-    <col min="27" max="27" width="20.44140625" style="3" customWidth="1"/>
-    <col min="28" max="28" width="24.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="24.6640625" style="3" customWidth="1"/>
-    <col min="32" max="35" width="18.5546875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="40" width="18.88671875" style="3" customWidth="1"/>
-    <col min="41" max="41" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="25" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="3" customWidth="1"/>
+    <col min="28" max="28" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="24.7109375" style="3" customWidth="1"/>
+    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="18.85546875" style="3" customWidth="1"/>
+    <col min="41" max="41" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="13" style="18" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="13" style="20" customWidth="1"/>
     <col min="46" max="46" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="24.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="16384" width="9.109375" style="3"/>
+    <col min="47" max="47" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="48" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="5" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8734,7 +8741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8751,23 +8758,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="7" customWidth="1"/>
-    <col min="2" max="3" width="25.6640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" style="7" customWidth="1"/>
-    <col min="6" max="7" width="15.6640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="25.6640625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" style="7" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="7" customWidth="1"/>
+    <col min="2" max="3" width="25.7109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="7" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="25.7109375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="7"/>
+    <col min="15" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>27</v>
       </c>
@@ -8811,7 +8818,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8826,25 +8833,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="16" customWidth="1"/>
     <col min="2" max="2" width="24" style="16" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5546875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.109375" style="16" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.6640625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="23" customWidth="1"/>
-    <col min="16" max="16" width="20.6640625" style="28" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="16"/>
+    <col min="3" max="3" width="25.5703125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5703125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.140625" style="16" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.7109375" style="17" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" style="23" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" style="28" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -8894,7 +8901,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:P2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8907,6 +8914,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -8917,15 +8933,6 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9032,6 +9039,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9044,14 +9059,6 @@
     <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBoe\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808C1457-7E6E-4AE4-847B-F90120CE08B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7237019-82AC-415E-B739-3B0BCE26D2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22305" yWindow="15" windowWidth="34035" windowHeight="21570" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="15" windowWidth="35070" windowHeight="21570" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -34,13 +34,13 @@
     <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AT$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AU$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$B$1:$Q$2</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
     <definedName name="CLINs">'[1]Options Lists'!$B$2:$B$5</definedName>
@@ -74,7 +74,7 @@
     <author>Lindsay Yorks</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="148">
   <si>
     <t>Start Date</t>
   </si>
@@ -759,6 +759,9 @@
   </si>
   <si>
     <t>Rationale</t>
+  </si>
+  <si>
+    <t>Task URL</t>
   </si>
 </sst>
 </file>
@@ -3031,7 +3034,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:AT1" sheet="BOEs"/>
+    <worksheetSource ref="C1:AU1" sheet="BOEs"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Type" numFmtId="49">
@@ -6045,18 +6048,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6064,24 +6068,27 @@
         <v>116</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
+  <autoFilter ref="A1:G1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
@@ -6092,28 +6099,29 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6121,51 +6129,54 @@
         <v>116</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
+  <autoFilter ref="A1:P1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8351,56 +8362,56 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="36" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="36" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="31" customWidth="1"/>
-    <col min="19" max="19" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="36" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="31" customWidth="1"/>
-    <col min="27" max="27" width="19" style="29" customWidth="1"/>
-    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.28515625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.85546875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="13" style="33" customWidth="1"/>
-    <col min="40" max="40" width="17" style="31" customWidth="1"/>
-    <col min="41" max="41" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.7109375" style="38" customWidth="1"/>
-    <col min="44" max="44" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.7109375" style="29" customWidth="1"/>
-    <col min="47" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="36" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="36" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" style="31" customWidth="1"/>
+    <col min="20" max="20" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" style="36" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.7109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="31" customWidth="1"/>
+    <col min="28" max="28" width="19" style="29" customWidth="1"/>
+    <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16.85546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="13" style="33" customWidth="1"/>
+    <col min="41" max="41" width="17" style="31" customWidth="1"/>
+    <col min="42" max="42" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="26.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.7109375" style="29" customWidth="1"/>
+    <col min="48" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8410,139 +8421,142 @@
       <c r="C1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="P1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="Q1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="S1" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="W1" s="35" t="s">
+      <c r="X1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="Y1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AA1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AB1" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AM1" s="32" t="s">
+      <c r="AN1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="AN1" s="30" t="s">
+      <c r="AO1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AO1" s="24" t="s">
+      <c r="AP1" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="AQ1" s="37" t="s">
+      <c r="AR1" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="AR1" s="37" t="s">
+      <c r="AS1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AS1" s="34" t="s">
+      <c r="AT1" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="AT1" s="27" t="s">
+      <c r="AU1" s="27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AT1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8555,7 +8569,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
@@ -8569,36 +8583,36 @@
     <col min="10" max="10" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.140625" style="20" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="20.140625" style="25" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="25" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="24.7109375" style="3" customWidth="1"/>
-    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="40" width="18.85546875" style="3" customWidth="1"/>
-    <col min="41" max="41" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="13" style="20" customWidth="1"/>
-    <col min="46" max="46" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="16384" width="9.140625" style="3"/>
+    <col min="14" max="15" width="20.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="25" customWidth="1"/>
+    <col min="28" max="28" width="20.42578125" style="3" customWidth="1"/>
+    <col min="29" max="29" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="24.7109375" style="3" customWidth="1"/>
+    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="41" width="18.85546875" style="3" customWidth="1"/>
+    <col min="42" max="42" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13" style="20" customWidth="1"/>
+    <col min="47" max="47" width="17" style="25" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8642,108 +8656,111 @@
         <v>102</v>
       </c>
       <c r="O1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Z1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="AA1" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AT1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="AT1" s="24" t="s">
+      <c r="AU1" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AU1" s="5" t="s">
+      <c r="AV1" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:AV1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8832,78 +8849,82 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" style="16" customWidth="1"/>
-    <col min="2" max="2" width="24" style="16" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5703125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.140625" style="16" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.7109375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" style="23" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="28" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="16"/>
+    <col min="1" max="1" width="18.42578125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="12" style="16" customWidth="1"/>
+    <col min="3" max="3" width="24" style="16" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.5703125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" style="16" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.140625" style="16" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.7109375" style="17" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" style="23" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" style="28" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="Q1" s="27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="B1:Q2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8914,15 +8935,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -8933,6 +8945,15 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9039,14 +9060,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9059,6 +9072,14 @@
     <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gitBoe\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7237019-82AC-415E-B739-3B0BCE26D2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1003C4AA-3F4E-4B6D-AE48-F5EE90B4C41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="15" windowWidth="35070" windowHeight="21570" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -24,20 +24,24 @@
     <sheet name="Resource Spreads" sheetId="41" r:id="rId9"/>
     <sheet name="MOQ by BOE by Task" sheetId="43" r:id="rId10"/>
     <sheet name="MOQ Table Data" sheetId="44" r:id="rId11"/>
-    <sheet name="WBS" sheetId="24" r:id="rId12"/>
-    <sheet name="User Permissions" sheetId="39" r:id="rId13"/>
-    <sheet name="CLINs" sheetId="25" r:id="rId14"/>
-    <sheet name="Workspace Identification" sheetId="40" r:id="rId15"/>
+    <sheet name="Current Skill Mix" sheetId="46" r:id="rId12"/>
+    <sheet name="Common Disclosure Skill Mix" sheetId="45" r:id="rId13"/>
+    <sheet name="WBS" sheetId="24" r:id="rId14"/>
+    <sheet name="User Permissions" sheetId="39" r:id="rId15"/>
+    <sheet name="CLINs" sheetId="25" r:id="rId16"/>
+    <sheet name="Workspace Identification" sheetId="40" r:id="rId17"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId16"/>
-    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Common Disclosure Skill Mix'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Current Skill Mix'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$B$1:$Q$2</definedName>
@@ -51,9 +55,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId18"/>
-    <pivotCache cacheId="1" r:id="rId19"/>
-    <pivotCache cacheId="2" r:id="rId20"/>
+    <pivotCache cacheId="33" r:id="rId20"/>
+    <pivotCache cacheId="34" r:id="rId21"/>
+    <pivotCache cacheId="35" r:id="rId22"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -318,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="158">
   <si>
     <t>Start Date</t>
   </si>
@@ -762,17 +766,49 @@
   </si>
   <si>
     <t>Task URL</t>
+  </si>
+  <si>
+    <t>Historical Hours</t>
+  </si>
+  <si>
+    <t>Labor Skill Mix</t>
+  </si>
+  <si>
+    <t>Included</t>
+  </si>
+  <si>
+    <t>BOE Skill Mix</t>
+  </si>
+  <si>
+    <t>Proposed Hours</t>
+  </si>
+  <si>
+    <t>Rationale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Resource	</t>
+  </si>
+  <si>
+    <t>Current Resource</t>
+  </si>
+  <si>
+    <t>Business Resource Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -940,7 +976,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
@@ -1042,6 +1078,17 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4238,7 +4285,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4587,7 +4634,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="34" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4796,7 +4843,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -6187,6 +6234,147 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC859F52-06EC-4D10-BF03-A04146FE2305}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="42" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{BC859F52-06EC-4D10-BF03-A04146FE2305}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:N1" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
@@ -6227,7 +6415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
@@ -6284,7 +6472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
@@ -6330,7 +6518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A18"/>
@@ -8935,28 +9123,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9059,32 +9225,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9101,4 +9264,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e309214\source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2EF835-5853-42D8-8A48-47D9C954658D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBEA335-0BD0-483F-946D-A300EB09BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="-14850" windowWidth="21600" windowHeight="11385" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -55,9 +55,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId20"/>
-    <pivotCache cacheId="4" r:id="rId21"/>
-    <pivotCache cacheId="5" r:id="rId22"/>
+    <pivotCache cacheId="12" r:id="rId20"/>
+    <pivotCache cacheId="13" r:id="rId21"/>
+    <pivotCache cacheId="14" r:id="rId22"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -979,7 +979,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
@@ -1092,6 +1092,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4288,7 +4289,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4637,7 +4638,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4846,7 +4847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8598,8 +8599,9 @@
     <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
     <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.7109375" style="29" customWidth="1"/>
-    <col min="48" max="16384" width="9.140625" style="1"/>
+    <col min="47" max="47" width="14.7109375" style="44" customWidth="1"/>
+    <col min="48" max="48" width="9.140625" style="29"/>
+    <col min="49" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9129,6 +9131,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9231,43 +9255,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9290,9 +9281,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e309214\source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBEA335-0BD0-483F-946D-A300EB09BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC7E66A-090D-4261-A63C-06A6D427DEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19395" windowHeight="15480" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -24,8 +24,8 @@
     <sheet name="Resource Spreads" sheetId="41" r:id="rId9"/>
     <sheet name="MOQ by BOE by Task" sheetId="43" r:id="rId10"/>
     <sheet name="MOQ Table Data" sheetId="44" r:id="rId11"/>
-    <sheet name="Current Skill Mix" sheetId="46" r:id="rId12"/>
-    <sheet name="Common Disclosure Skill Mix" sheetId="45" r:id="rId13"/>
+    <sheet name="Legacy Skill Mix" sheetId="46" r:id="rId12"/>
+    <sheet name="LM Enterprise Skill Mix" sheetId="45" r:id="rId13"/>
     <sheet name="WBS" sheetId="24" r:id="rId14"/>
     <sheet name="User Permissions" sheetId="39" r:id="rId15"/>
     <sheet name="CLINs" sheetId="25" r:id="rId16"/>
@@ -40,8 +40,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Common Disclosure Skill Mix'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Current Skill Mix'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legacy Skill Mix'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'LM Enterprise Skill Mix'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$B$1:$Q$2</definedName>
@@ -55,9 +55,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId20"/>
-    <pivotCache cacheId="13" r:id="rId21"/>
-    <pivotCache cacheId="14" r:id="rId22"/>
+    <pivotCache cacheId="0" r:id="rId20"/>
+    <pivotCache cacheId="1" r:id="rId21"/>
+    <pivotCache cacheId="2" r:id="rId22"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4638,7 +4638,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4847,7 +4847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -9131,28 +9131,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9255,10 +9233,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9281,20 +9292,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC7E66A-090D-4261-A63C-06A6D427DEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F782E-226E-48EB-BF8E-0BAE33754DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19395" windowHeight="15480" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -36,8 +36,8 @@
     <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AV$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AU$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legacy Skill Mix'!$A$1:$M$1</definedName>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="158">
   <si>
     <t>Start Date</t>
   </si>
@@ -601,9 +601,6 @@
   </si>
   <si>
     <t>Month</t>
-  </si>
-  <si>
-    <t>Historical Metrics</t>
   </si>
   <si>
     <t>Perf Org Description</t>
@@ -3085,7 +3082,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:AU1" sheet="BOEs"/>
+    <worksheetSource ref="C1:AT1" sheet="BOEs"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Type" numFmtId="49">
@@ -6116,10 +6113,10 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -6128,13 +6125,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>85</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6177,10 +6174,10 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -6192,37 +6189,37 @@
         <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="Q1" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6262,10 +6259,10 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -6277,25 +6274,25 @@
         <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H1" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="J1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="L1" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6332,10 +6329,10 @@
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -6347,28 +6344,28 @@
         <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="I1" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="32" t="s">
-        <v>149</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L1" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6404,7 +6401,7 @@
         <v>69</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
@@ -6453,7 +6450,7 @@
         <v>65</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>75</v>
@@ -6462,7 +6459,7 @@
         <v>76</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -6492,7 +6489,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>29</v>
@@ -6507,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
@@ -6546,22 +6543,22 @@
     </row>
     <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6581,12 +6578,12 @@
     </row>
     <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6596,7 +6593,7 @@
     </row>
     <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6606,17 +6603,17 @@
     </row>
     <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -8554,7 +8551,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
@@ -8578,44 +8575,43 @@
     <col min="20" max="20" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.7109375" style="36" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.7109375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="31" customWidth="1"/>
-    <col min="28" max="28" width="19" style="29" customWidth="1"/>
-    <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.85546875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16.85546875" style="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="33" customWidth="1"/>
-    <col min="41" max="41" width="17" style="31" customWidth="1"/>
-    <col min="42" max="42" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.7109375" style="44" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" style="29"/>
-    <col min="49" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="13.7109375" style="36" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="31" customWidth="1"/>
+    <col min="27" max="27" width="19" style="29" customWidth="1"/>
+    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.28515625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.85546875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.85546875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="33" customWidth="1"/>
+    <col min="40" max="40" width="17" style="31" customWidth="1"/>
+    <col min="41" max="41" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.7109375" style="38" customWidth="1"/>
+    <col min="44" max="44" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="14.7109375" style="44" customWidth="1"/>
+    <col min="47" max="47" width="9.140625" style="29"/>
+    <col min="48" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -8624,13 +8620,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>88</v>
@@ -8642,7 +8638,7 @@
         <v>28</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>29</v>
@@ -8657,49 +8653,49 @@
         <v>32</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S1" s="30" t="s">
         <v>87</v>
       </c>
       <c r="T1" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="W1" s="5" t="s">
-        <v>93</v>
+      <c r="W1" s="35" t="s">
+        <v>4</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="Z1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA1" s="30" t="s">
+      <c r="Y1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AB1" s="24" t="s">
+      <c r="AA1" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB1" s="5" t="s">
         <v>103</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="AG1" s="5" t="s">
         <v>142</v>
@@ -8711,48 +8707,45 @@
         <v>144</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="AL1" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AM1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AN1" s="32" t="s">
+      <c r="AM1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="AO1" s="30" t="s">
+      <c r="AN1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="24" t="s">
+      <c r="AO1" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ1" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR1" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS1" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="AQ1" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR1" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="AS1" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT1" s="34" t="s">
+      <c r="AT1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="AU1" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="AU1" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="AV1" s="27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AV2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="A1:AU2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8765,7 +8758,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
@@ -8786,34 +8779,33 @@
     <col min="19" max="19" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="25" customWidth="1"/>
-    <col min="28" max="28" width="20.42578125" style="3" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="24.7109375" style="3" customWidth="1"/>
-    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="41" width="18.85546875" style="3" customWidth="1"/>
-    <col min="42" max="42" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13" style="20" customWidth="1"/>
-    <col min="47" max="47" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.140625" style="3"/>
+    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="25" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="3" customWidth="1"/>
+    <col min="28" max="28" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="24.7109375" style="3" customWidth="1"/>
+    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="18.85546875" style="3" customWidth="1"/>
+    <col min="41" max="41" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13" style="20" customWidth="1"/>
+    <col min="46" max="46" width="17" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="48" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>26</v>
@@ -8837,22 +8829,22 @@
         <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K1" s="19" t="s">
         <v>87</v>
       </c>
       <c r="L1" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="O1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>2</v>
@@ -8864,46 +8856,46 @@
         <v>84</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>85</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z1" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="Z1" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>103</v>
       </c>
       <c r="AB1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="AD1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AE1" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="AF1" s="5" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="AG1" s="5" t="s">
         <v>142</v>
@@ -8915,13 +8907,13 @@
         <v>144</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="AL1" s="5" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AM1" s="5" t="s">
         <v>107</v>
@@ -8930,33 +8922,30 @@
         <v>108</v>
       </c>
       <c r="AO1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS1" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT1" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="AP1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AS1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT1" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AU1" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="AV1" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="AU1" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AV1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8995,7 +8984,7 @@
         <v>28</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>29</v>
@@ -9013,10 +9002,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>66</v>
@@ -9025,10 +9014,10 @@
         <v>67</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
@@ -9067,7 +9056,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -9097,10 +9086,10 @@
         <v>89</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>11</v>
@@ -9112,10 +9101,10 @@
         <v>92</v>
       </c>
       <c r="P1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q1" s="27" t="s">
         <v>111</v>
-      </c>
-      <c r="Q1" s="27" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -9131,6 +9120,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9233,43 +9244,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9292,9 +9270,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\IES\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F782E-226E-48EB-BF8E-0BAE33754DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96088262-8478-48E8-A7D8-ED2D92AC6608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15105" yWindow="-21720" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AU$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AV$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
@@ -55,9 +55,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId20"/>
-    <pivotCache cacheId="1" r:id="rId21"/>
-    <pivotCache cacheId="2" r:id="rId22"/>
+    <pivotCache cacheId="48" r:id="rId20"/>
+    <pivotCache cacheId="49" r:id="rId21"/>
+    <pivotCache cacheId="50" r:id="rId22"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="159">
   <si>
     <t>Start Date</t>
   </si>
@@ -796,6 +796,9 @@
   </si>
   <si>
     <t>UCOT Hours</t>
+  </si>
+  <si>
+    <t>Task Author</t>
   </si>
 </sst>
 </file>
@@ -4286,7 +4289,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4635,7 +4638,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4844,7 +4847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="50" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8551,56 +8554,56 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="36" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="36" customWidth="1"/>
-    <col min="18" max="18" width="21.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" style="31" customWidth="1"/>
-    <col min="20" max="20" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="36" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="31" customWidth="1"/>
-    <col min="27" max="27" width="19" style="29" customWidth="1"/>
-    <col min="28" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.28515625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.85546875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="13" style="33" customWidth="1"/>
-    <col min="40" max="40" width="17" style="31" customWidth="1"/>
-    <col min="41" max="41" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.7109375" style="38" customWidth="1"/>
-    <col min="44" max="44" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.7109375" style="44" customWidth="1"/>
-    <col min="47" max="47" width="9.140625" style="29"/>
-    <col min="48" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="7" width="13.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="36" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="36" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" style="31" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" style="36" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.7109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="31" customWidth="1"/>
+    <col min="28" max="28" width="19" style="29" customWidth="1"/>
+    <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16.85546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="13" style="33" customWidth="1"/>
+    <col min="41" max="41" width="17" style="31" customWidth="1"/>
+    <col min="42" max="42" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="26.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="14.7109375" style="44" customWidth="1"/>
+    <col min="48" max="48" width="9.140625" style="29"/>
+    <col min="49" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8619,133 +8622,136 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="Q1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="R1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="T1" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="U1" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="W1" s="35" t="s">
+      <c r="X1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="Y1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AA1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AB1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AM1" s="32" t="s">
+      <c r="AN1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="AN1" s="30" t="s">
+      <c r="AO1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AO1" s="24" t="s">
+      <c r="AP1" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="AQ1" s="37" t="s">
+      <c r="AR1" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="AR1" s="37" t="s">
+      <c r="AS1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AS1" s="34" t="s">
+      <c r="AT1" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="AU1" s="27" t="s">
+      <c r="AV1" s="27" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AU2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="A1:AV2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\IES\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e426263\source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96088262-8478-48E8-A7D8-ED2D92AC6608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34083DD1-6AF8-428E-8120-B3C2519D84A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15105" yWindow="-21720" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AV$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AW$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
@@ -55,9 +55,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId20"/>
-    <pivotCache cacheId="49" r:id="rId21"/>
-    <pivotCache cacheId="50" r:id="rId22"/>
+    <pivotCache cacheId="0" r:id="rId20"/>
+    <pivotCache cacheId="1" r:id="rId21"/>
+    <pivotCache cacheId="2" r:id="rId22"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="159">
   <si>
     <t>Start Date</t>
   </si>
@@ -4289,7 +4289,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4638,7 +4638,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4847,7 +4847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="50" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8554,7 +8554,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AW2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
@@ -8598,12 +8598,13 @@
     <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
     <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.7109375" style="44" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" style="29"/>
-    <col min="49" max="16384" width="9.140625" style="1"/>
+    <col min="47" max="47" width="16.140625" style="44" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.140625" style="44" customWidth="1"/>
+    <col min="49" max="49" width="9.140625" style="29"/>
+    <col min="50" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8745,13 +8746,16 @@
       <c r="AU1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="AV1" s="27" t="s">
+      <c r="AV1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW1" s="27" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AV2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="A1:AW2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -9126,28 +9130,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9250,10 +9232,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9276,20 +9291,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e426263\source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34083DD1-6AF8-428E-8120-B3C2519D84A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13764607-55C8-4153-9C9D-2B561F791C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14025" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -9130,6 +9130,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9232,43 +9254,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9291,9 +9280,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e426263\source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13764607-55C8-4153-9C9D-2B561F791C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D82D017-A0B6-46B0-867F-A9EE31C5A497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14025" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -37,7 +37,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AW$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AU$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legacy Skill Mix'!$A$1:$M$1</definedName>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="159">
   <si>
     <t>Start Date</t>
   </si>
@@ -3085,7 +3085,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lindsay Yorks" refreshedDate="40653.729487847224" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:AT1" sheet="BOEs"/>
+    <worksheetSource ref="C1:AU1" sheet="BOEs"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Type" numFmtId="49">
@@ -8561,7 +8561,8 @@
     <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
@@ -8768,7 +8769,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
@@ -8786,31 +8787,32 @@
     <col min="16" max="16" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="25" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="24.7109375" style="3" customWidth="1"/>
-    <col min="32" max="35" width="18.5703125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="40" width="18.85546875" style="3" customWidth="1"/>
-    <col min="41" max="41" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="13" style="20" customWidth="1"/>
-    <col min="46" max="46" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="16384" width="9.140625" style="3"/>
+    <col min="19" max="19" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.42578125" style="25" customWidth="1"/>
+    <col min="28" max="28" width="20.42578125" style="3" customWidth="1"/>
+    <col min="29" max="29" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="24.7109375" style="3" customWidth="1"/>
+    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="41" width="18.85546875" style="3" customWidth="1"/>
+    <col min="42" max="42" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13" style="18" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13" style="20" customWidth="1"/>
+    <col min="47" max="47" width="17" style="25" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8865,97 +8867,100 @@
       <c r="R1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Z1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="AA1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AT1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="AT1" s="24" t="s">
+      <c r="AU1" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="AU1" s="5" t="s">
+      <c r="AV1" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AU1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:AV1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D82D017-A0B6-46B0-867F-A9EE31C5A497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C551256-D243-4F3B-BD62-711C3C5C6A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15510" yWindow="0" windowWidth="19410" windowHeight="15480" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -24,27 +24,25 @@
     <sheet name="Resource Spreads" sheetId="41" r:id="rId9"/>
     <sheet name="MOQ by BOE by Task" sheetId="43" r:id="rId10"/>
     <sheet name="MOQ Table Data" sheetId="44" r:id="rId11"/>
-    <sheet name="Legacy Skill Mix" sheetId="46" r:id="rId12"/>
-    <sheet name="LM Enterprise Skill Mix" sheetId="45" r:id="rId13"/>
-    <sheet name="WBS" sheetId="24" r:id="rId14"/>
-    <sheet name="User Permissions" sheetId="39" r:id="rId15"/>
-    <sheet name="CLINs" sheetId="25" r:id="rId16"/>
-    <sheet name="Workspace Identification" sheetId="40" r:id="rId17"/>
+    <sheet name="Skill Mix Summary" sheetId="45" r:id="rId12"/>
+    <sheet name="WBS" sheetId="24" r:id="rId13"/>
+    <sheet name="User Permissions" sheetId="39" r:id="rId14"/>
+    <sheet name="CLINs" sheetId="25" r:id="rId15"/>
+    <sheet name="Workspace Identification" sheetId="40" r:id="rId16"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
-    <externalReference r:id="rId19"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BOE &amp; Resource Combo'!$A$1:$AW$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">BOEs!$A$1:$AV$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BOEs (2)'!$B$1:$T$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BOEs (3)'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legacy Skill Mix'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'LM Enterprise Skill Mix'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'MOQ by BOE by Task'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MOQ Table Data'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Resource Spreads'!$B$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Skill Mix Summary'!$A$1:$Q$1</definedName>
     <definedName name="Approvers">'[1]Options Lists'!$D$2:$D$4</definedName>
     <definedName name="Authors">'[1]Options Lists'!$C$2:$C$4</definedName>
     <definedName name="CLINs">'[1]Options Lists'!$B$2:$B$5</definedName>
@@ -55,9 +53,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId20"/>
-    <pivotCache cacheId="1" r:id="rId21"/>
-    <pivotCache cacheId="2" r:id="rId22"/>
+    <pivotCache cacheId="0" r:id="rId19"/>
+    <pivotCache cacheId="1" r:id="rId20"/>
+    <pivotCache cacheId="2" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -322,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="159">
   <si>
     <t>Start Date</t>
   </si>
@@ -768,27 +766,9 @@
     <t>Historical Hours</t>
   </si>
   <si>
-    <t>Labor Skill Mix</t>
-  </si>
-  <si>
-    <t>Included</t>
-  </si>
-  <si>
-    <t>BOE Skill Mix</t>
-  </si>
-  <si>
-    <t>Proposed Hours</t>
-  </si>
-  <si>
     <t>Rationale </t>
   </si>
   <si>
-    <t xml:space="preserve">Included </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Resource	</t>
-  </si>
-  <si>
     <t>Current Resource</t>
   </si>
   <si>
@@ -799,19 +779,36 @@
   </si>
   <si>
     <t>Task Author</t>
+  </si>
+  <si>
+    <t>Historical Skill Mix</t>
+  </si>
+  <si>
+    <t>Proposed Skill Mix</t>
+  </si>
+  <si>
+    <t>Proposed Legacy Resource</t>
+  </si>
+  <si>
+    <t>Proposed BRC</t>
+  </si>
+  <si>
+    <t>Total Proposed Legacy &amp; BRC</t>
+  </si>
+  <si>
+    <t>Grand Total Hours</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -979,7 +976,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
@@ -1085,10 +1082,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6238,77 +6231,8 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC859F52-06EC-4D10-BF03-A04146FE2305}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="42" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="43" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="H1" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="K1" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{BC859F52-06EC-4D10-BF03-A04146FE2305}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -6320,14 +6244,15 @@
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" style="43" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" style="33" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" style="33" customWidth="1"/>
+    <col min="12" max="12" width="29.28515625" style="42" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="29.5703125" style="41" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6347,38 +6272,47 @@
         <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I1" s="39" t="s">
         <v>147</v>
       </c>
       <c r="J1" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
@@ -6419,7 +6353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
@@ -6476,7 +6410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
@@ -6522,7 +6456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:A18"/>
@@ -8599,8 +8533,8 @@
     <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
     <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.140625" style="44" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.140625" style="44" customWidth="1"/>
+    <col min="47" max="47" width="16.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.140625" style="42" customWidth="1"/>
     <col min="49" max="49" width="9.140625" style="29"/>
     <col min="50" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -8625,7 +8559,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>122</v>
@@ -8745,7 +8679,7 @@
         <v>110</v>
       </c>
       <c r="AU1" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AV1" s="5" t="s">
         <v>6</v>
@@ -8868,7 +8802,7 @@
         <v>84</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>122</v>
@@ -9135,28 +9069,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9259,32 +9171,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9301,4 +9210,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Code Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C551256-D243-4F3B-BD62-711C3C5C6A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77217A20-C28B-47A9-A0B5-98BE70C78952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15510" yWindow="0" windowWidth="19410" windowHeight="15480" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="960" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -803,12 +803,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1078,14 +1077,14 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6243,12 +6242,12 @@
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="41" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.140625" style="33" customWidth="1"/>
     <col min="11" max="11" width="22.140625" style="33" customWidth="1"/>
-    <col min="12" max="12" width="29.28515625" style="42" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="29.5703125" style="41" customWidth="1"/>
+    <col min="12" max="12" width="29.28515625" style="41" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="29.5703125" style="42" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6277,7 +6276,7 @@
       <c r="H1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="40" t="s">
         <v>147</v>
       </c>
       <c r="J1" s="32" t="s">
@@ -6286,19 +6285,19 @@
       <c r="K1" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="40" t="s">
         <v>158</v>
       </c>
       <c r="Q1" s="5" t="s">
@@ -6309,6 +6308,7 @@
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8533,8 +8533,8 @@
     <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
     <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.140625" style="42" customWidth="1"/>
+    <col min="47" max="47" width="16.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.140625" style="39" customWidth="1"/>
     <col min="49" max="49" width="9.140625" style="29"/>
     <col min="50" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -9172,15 +9172,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -9191,6 +9182,15 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9213,14 +9213,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9235,4 +9227,12 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Code Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77217A20-C28B-47A9-A0B5-98BE70C78952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810E7EBD-C9E0-4920-95DE-E2396B44CD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="960" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -9069,6 +9069,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9171,19 +9184,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9194,6 +9194,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9212,23 +9229,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
   <ds:schemaRefs>

--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Code Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C551256-D243-4F3B-BD62-711C3C5C6A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90436C3F-DCDE-443C-9A0B-913A2BB8CDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15510" yWindow="0" windowWidth="19410" windowHeight="15480" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -803,12 +803,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1078,14 +1077,14 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6243,12 +6242,12 @@
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="41" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.140625" style="33" customWidth="1"/>
     <col min="11" max="11" width="22.140625" style="33" customWidth="1"/>
-    <col min="12" max="12" width="29.28515625" style="42" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="29.5703125" style="41" customWidth="1"/>
+    <col min="12" max="12" width="29.28515625" style="41" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="29.5703125" style="42" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6277,7 +6276,7 @@
       <c r="H1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="40" t="s">
         <v>147</v>
       </c>
       <c r="J1" s="32" t="s">
@@ -6286,19 +6285,19 @@
       <c r="K1" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="40" t="s">
         <v>158</v>
       </c>
       <c r="Q1" s="5" t="s">
@@ -8533,8 +8532,8 @@
     <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
     <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.140625" style="42" customWidth="1"/>
+    <col min="47" max="47" width="16.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.140625" style="39" customWidth="1"/>
     <col min="49" max="49" width="9.140625" style="29"/>
     <col min="50" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -9172,15 +9171,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
@@ -9191,6 +9181,15 @@
     </SipLabel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9213,14 +9212,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9235,4 +9226,12 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataSpaceSystems.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e405721\Code Repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e402751\Project\FB&amp;I\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810E7EBD-C9E0-4920-95DE-E2396B44CD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF797106-F36B-4301-B92D-7A75E3933144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1250" yWindow="1130" windowWidth="17060" windowHeight="8660" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -53,9 +53,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId19"/>
-    <pivotCache cacheId="1" r:id="rId20"/>
-    <pivotCache cacheId="2" r:id="rId21"/>
+    <pivotCache cacheId="6" r:id="rId19"/>
+    <pivotCache cacheId="7" r:id="rId20"/>
+    <pivotCache cacheId="8" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="160">
   <si>
     <t>Start Date</t>
   </si>
@@ -797,6 +797,9 @@
   </si>
   <si>
     <t>Grand Total Hours</t>
+  </si>
+  <si>
+    <t>Current Workspace</t>
   </si>
 </sst>
 </file>
@@ -4281,7 +4284,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4630,7 +4633,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4839,7 +4842,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -5570,25 +5573,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:N32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
@@ -5632,7 +5635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -5676,7 +5679,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G6" t="s">
         <v>57</v>
       </c>
@@ -5702,7 +5705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H8" t="s">
         <v>43</v>
       </c>
@@ -5725,7 +5728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>62</v>
       </c>
@@ -5760,7 +5763,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G12" t="s">
         <v>57</v>
       </c>
@@ -5786,7 +5789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H14" t="s">
         <v>43</v>
       </c>
@@ -5809,7 +5812,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>57</v>
       </c>
@@ -5844,7 +5847,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -5888,7 +5891,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G20" t="s">
         <v>57</v>
       </c>
@@ -5914,7 +5917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H22" t="s">
         <v>43</v>
       </c>
@@ -5937,7 +5940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H24" t="s">
         <v>55</v>
       </c>
@@ -5960,7 +5963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H26" t="s">
         <v>51</v>
       </c>
@@ -5983,7 +5986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>64</v>
       </c>
@@ -6018,7 +6021,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="G30" t="s">
         <v>57</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>62</v>
       </c>
@@ -6092,18 +6095,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13AD99-C0B6-4E90-ABF6-10E14BCDEE02}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="64.140625" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6129,7 +6132,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{9706A812-64F4-4103-BF42-450B5D5EA342}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6143,28 +6146,28 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB92274E-9194-432C-BABA-DBDF288E7F50}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.54296875" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.453125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="5" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6217,7 +6220,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{B03D36E4-F111-482D-8BA5-A875D16A6E86}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6232,26 +6235,26 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" style="33" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" style="33" customWidth="1"/>
-    <col min="12" max="12" width="29.28515625" style="41" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="29.5703125" style="42" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.1796875" style="33" customWidth="1"/>
+    <col min="11" max="11" width="22.1796875" style="33" customWidth="1"/>
+    <col min="12" max="12" width="29.26953125" style="41" customWidth="1"/>
+    <col min="13" max="13" width="19.26953125" style="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="29.54296875" style="42" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -6304,7 +6307,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{5AF11AB7-F45F-4865-B8BC-DBCCDB5DD031}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6316,15 +6319,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="4" width="30.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="33.140625" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="30.7265625" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="30.7265625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.1796875" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
@@ -6341,7 +6344,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:5" ht="13.5" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6357,20 +6360,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
-    <col min="2" max="3" width="35.7109375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="18.81640625" style="15" customWidth="1"/>
+    <col min="2" max="3" width="35.7265625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="26.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="14" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="14" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -6399,7 +6402,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6414,17 +6417,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" style="8" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="13.1796875" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="50.7265625" style="8" customWidth="1"/>
+    <col min="4" max="5" width="20.7265625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>98</v>
       </c>
@@ -6444,7 +6447,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6459,98 +6462,103 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="82.140625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="32.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="82.1796875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -6567,28 +6575,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13.5703125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="3"/>
+    <col min="15" max="17" width="13.54296875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
@@ -6632,7 +6640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>59</v>
       </c>
@@ -6643,7 +6651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>59</v>
       </c>
@@ -6666,7 +6674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -6707,7 +6715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
@@ -6748,7 +6756,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>59</v>
       </c>
@@ -6771,7 +6779,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>59</v>
       </c>
@@ -6812,7 +6820,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
@@ -6853,7 +6861,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -6873,7 +6881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
@@ -6896,7 +6904,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>60</v>
       </c>
@@ -6937,7 +6945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>60</v>
       </c>
@@ -6978,7 +6986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -7019,7 +7027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
@@ -7060,7 +7068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>60</v>
       </c>
@@ -7083,7 +7091,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>60</v>
       </c>
@@ -7139,20 +7147,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" customWidth="1"/>
     <col min="9" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -7178,7 +7186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -7204,7 +7212,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -7212,7 +7220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7238,12 +7246,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>45</v>
       </c>
@@ -7251,7 +7259,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -7277,12 +7285,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>45</v>
       </c>
@@ -7304,29 +7312,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:T32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
@@ -7388,7 +7396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -7450,7 +7458,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>34</v>
       </c>
@@ -7509,7 +7517,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="I8" t="s">
         <v>40</v>
       </c>
@@ -7547,7 +7555,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -7606,7 +7614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="R12" t="s">
         <v>20</v>
       </c>
@@ -7617,7 +7625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="N14" t="s">
         <v>43</v>
       </c>
@@ -7640,7 +7648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="O16" t="s">
         <v>53</v>
       </c>
@@ -7660,7 +7668,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -7722,7 +7730,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -7781,7 +7789,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="I22" t="s">
         <v>49</v>
       </c>
@@ -7819,7 +7827,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -7878,7 +7886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="O26" t="s">
         <v>52</v>
       </c>
@@ -7898,7 +7906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="N28" t="s">
         <v>43</v>
       </c>
@@ -7921,7 +7929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="N30" t="s">
         <v>55</v>
       </c>
@@ -7944,7 +7952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="N32" t="s">
         <v>51</v>
       </c>
@@ -7981,33 +7989,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:T16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="3" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="3"/>
+    <col min="2" max="3" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13.5703125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="3"/>
+    <col min="21" max="23" width="13.54296875" style="3" customWidth="1"/>
+    <col min="24" max="24" width="15.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>70</v>
       </c>
@@ -8069,7 +8077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>58</v>
       </c>
@@ -8095,7 +8103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
@@ -8118,7 +8126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
@@ -8147,7 +8155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>58</v>
       </c>
@@ -8176,7 +8184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>58</v>
       </c>
@@ -8199,7 +8207,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -8228,7 +8236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -8257,7 +8265,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -8283,7 +8291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -8306,7 +8314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -8335,7 +8343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -8364,7 +8372,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -8393,7 +8401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -8422,7 +8430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -8445,7 +8453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -8489,57 +8497,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AW2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="36" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="36" customWidth="1"/>
-    <col min="19" max="19" width="21.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="20.140625" style="31" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.7109375" style="36" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.7109375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="31" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.54296875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.7265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.54296875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.453125" style="36" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" style="36" customWidth="1"/>
+    <col min="19" max="19" width="21.453125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" style="31" customWidth="1"/>
+    <col min="21" max="21" width="18.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7265625" style="36" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.7265625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="20.453125" style="31" customWidth="1"/>
     <col min="28" max="28" width="19" style="29" customWidth="1"/>
     <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.85546875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16.85546875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="24.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.26953125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="18.54296875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.81640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16.81640625" style="1" customWidth="1"/>
     <col min="40" max="40" width="13" style="33" customWidth="1"/>
     <col min="41" max="41" width="17" style="31" customWidth="1"/>
-    <col min="42" max="42" width="15.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.7109375" style="38" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="26.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.7265625" style="38" customWidth="1"/>
+    <col min="45" max="45" width="10.54296875" style="38" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.140625" style="39" customWidth="1"/>
-    <col min="49" max="49" width="9.140625" style="29"/>
-    <col min="50" max="16384" width="9.140625" style="1"/>
+    <col min="47" max="47" width="16.1796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.1796875" style="39" customWidth="1"/>
+    <col min="49" max="49" width="9.1796875" style="29"/>
+    <col min="50" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" s="5" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8688,7 +8696,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:49" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:AW2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8704,49 +8712,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AV2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="20.140625" style="25" customWidth="1"/>
-    <col min="14" max="15" width="20.140625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.1796875" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="20.1796875" style="25" customWidth="1"/>
+    <col min="14" max="15" width="20.1796875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" style="25" customWidth="1"/>
-    <col min="28" max="28" width="20.42578125" style="3" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="24.7109375" style="3" customWidth="1"/>
-    <col min="33" max="36" width="18.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="41" width="18.85546875" style="3" customWidth="1"/>
-    <col min="42" max="42" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.7265625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="20.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.453125" style="25" customWidth="1"/>
+    <col min="28" max="28" width="20.453125" style="3" customWidth="1"/>
+    <col min="29" max="29" width="24.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="24.7265625" style="3" customWidth="1"/>
+    <col min="33" max="36" width="18.54296875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="41" width="18.81640625" style="3" customWidth="1"/>
+    <col min="42" max="42" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="13" style="18" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="13" style="20" customWidth="1"/>
     <col min="47" max="47" width="17" style="25" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.140625" style="3"/>
+    <col min="48" max="48" width="24.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="5" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="5" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
@@ -8892,7 +8900,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:48" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:48" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:AV1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8909,23 +8917,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="7" customWidth="1"/>
-    <col min="2" max="3" width="25.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="7" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="25.7109375" style="7" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" style="7" customWidth="1"/>
+    <col min="2" max="3" width="25.7265625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" style="7" customWidth="1"/>
+    <col min="6" max="7" width="15.7265625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="25.7265625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="16.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="7"/>
+    <col min="15" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="9" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>27</v>
       </c>
@@ -8969,7 +8977,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8984,26 +8992,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" style="16" customWidth="1"/>
     <col min="2" max="2" width="12" style="16" customWidth="1"/>
     <col min="3" max="3" width="24" style="16" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.5703125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="18.140625" style="16" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.7109375" style="17" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="23" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" style="28" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="16"/>
+    <col min="4" max="4" width="25.54296875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.54296875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="20.453125" style="16" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.1796875" style="16" customWidth="1"/>
+    <col min="13" max="13" width="18.81640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.7265625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="20.7265625" style="23" customWidth="1"/>
+    <col min="17" max="17" width="20.7265625" style="28" customWidth="1"/>
+    <col min="18" max="16384" width="9.1796875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>146</v>
       </c>
@@ -9056,7 +9064,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="B1:Q2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9082,6 +9090,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9184,15 +9201,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
   <ds:schemaRefs>
@@ -9211,6 +9219,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9227,12 +9243,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>